--- a/cucumber-for-appian/src/test/resources/testdata/End2End/01_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/01_NovatedApp_End2End.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="111">
   <si>
     <t>TC ID</t>
   </si>
@@ -140,6 +140,9 @@
     <t>Reimbursement Claim</t>
   </si>
   <si>
+    <t>5591</t>
+  </si>
+  <si>
     <t>Fuel</t>
   </si>
   <si>
@@ -149,6 +152,48 @@
     <t>N/A</t>
   </si>
   <si>
+    <t>16 Jun 2026</t>
+  </si>
+  <si>
+    <t>2 Jun 2026</t>
+  </si>
+  <si>
+    <t>REQ-986</t>
+  </si>
+  <si>
+    <t>Mr</t>
+  </si>
+  <si>
+    <t>Toshihiko</t>
+  </si>
+  <si>
+    <t>Inafune</t>
+  </si>
+  <si>
+    <t>05 Jun 1995</t>
+  </si>
+  <si>
+    <t>0469750861</t>
+  </si>
+  <si>
+    <t>inafune@jfcaust.com.au.test</t>
+  </si>
+  <si>
+    <t>Your Residential Address *</t>
+  </si>
+  <si>
+    <t>JFC Australia Co Pty Ltd</t>
+  </si>
+  <si>
+    <t>FTV21M</t>
+  </si>
+  <si>
+    <t>MAZDA CX-5</t>
+  </si>
+  <si>
+    <t>30 Aug 2029</t>
+  </si>
+  <si>
     <t>TC002</t>
   </si>
   <si>
@@ -218,64 +263,103 @@
     <t>${TC001.Lease End Date}</t>
   </si>
   <si>
-    <t>FTV21M</t>
-  </si>
-  <si>
-    <t>MAZDA CX-5</t>
-  </si>
-  <si>
-    <t>30 Aug 2029</t>
-  </si>
-  <si>
-    <t>12316</t>
-  </si>
-  <si>
-    <t>Mr</t>
-  </si>
-  <si>
-    <t>Toshihiko</t>
-  </si>
-  <si>
-    <t>Inafune</t>
-  </si>
-  <si>
-    <t>05/06/1995</t>
-  </si>
-  <si>
-    <t>0469750861</t>
-  </si>
-  <si>
-    <t>inafune@jfcaust.com.au.test</t>
-  </si>
-  <si>
-    <t>Your Residential Address *</t>
-  </si>
-  <si>
-    <t>JFC Australia Co Pty Ltd</t>
-  </si>
-  <si>
-    <t>19 May 2026</t>
-  </si>
-  <si>
-    <t>REQ-714</t>
-  </si>
-  <si>
-    <t>12317</t>
-  </si>
-  <si>
-    <t>REQ-719</t>
-  </si>
-  <si>
-    <t>12318</t>
-  </si>
-  <si>
-    <t>REQ-722</t>
-  </si>
-  <si>
-    <t>12319</t>
-  </si>
-  <si>
-    <t>REQ-729</t>
+    <t>5592</t>
+  </si>
+  <si>
+    <t>REQ-987</t>
+  </si>
+  <si>
+    <t>CYP806</t>
+  </si>
+  <si>
+    <t>TESLA MODEL Y</t>
+  </si>
+  <si>
+    <t>11 Jun 2027</t>
+  </si>
+  <si>
+    <t>8002</t>
+  </si>
+  <si>
+    <t>Neeti</t>
+  </si>
+  <si>
+    <t>Tripathi</t>
+  </si>
+  <si>
+    <t>03 Jul 1993</t>
+  </si>
+  <si>
+    <t>0499656877</t>
+  </si>
+  <si>
+    <t>neeti.tripathi@kmart.com.au.test</t>
+  </si>
+  <si>
+    <t>Kmart Australia Limited</t>
+  </si>
+  <si>
+    <t>13 Jul 2026</t>
+  </si>
+  <si>
+    <t>22 Jul 2026</t>
+  </si>
+  <si>
+    <t>REQ-97</t>
+  </si>
+  <si>
+    <t>8061</t>
+  </si>
+  <si>
+    <t>28 Jul 2026</t>
+  </si>
+  <si>
+    <t>29 Jul 2026</t>
+  </si>
+  <si>
+    <t>REQ-157</t>
+  </si>
+  <si>
+    <t>Notifications (0)</t>
+  </si>
+  <si>
+    <t>There are no Current quotes to display</t>
+  </si>
+  <si>
+    <t>134444</t>
+  </si>
+  <si>
+    <t>19 Jul 2026</t>
+  </si>
+  <si>
+    <t>20 Aug 2026</t>
+  </si>
+  <si>
+    <t>134445</t>
+  </si>
+  <si>
+    <t>134446</t>
+  </si>
+  <si>
+    <t>REQ-1651</t>
+  </si>
+  <si>
+    <t>134447</t>
+  </si>
+  <si>
+    <t>REQ-1652</t>
+  </si>
+  <si>
+    <t>134448</t>
+  </si>
+  <si>
+    <t>REQ-1653</t>
+  </si>
+  <si>
+    <t>134451</t>
+  </si>
+  <si>
+    <t>24 Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -1430,213 +1514,213 @@
         <v>36</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="D2" s="6" t="n">
         <f>C2+1</f>
-        <v>12320.0</v>
+        <v>134452.0</v>
       </c>
       <c r="E2" s="6" t="n">
         <f>D2</f>
-        <v>12320.0</v>
+        <v>134452.0</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="4">
         <v>400</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="V2" s="7" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>12,320 km</v>
+        <v>134,452 km</v>
       </c>
       <c r="W2" s="7" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="X2" s="7" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="Y2" s="7" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="Z2" s="7" t="str">
         <f>_xlfn.CONCAT(X2," ",Y2)</f>
         <v>Toshihiko Inafune</v>
       </c>
       <c r="AA2" s="7" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="AB2" s="7" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="AE2" s="7" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="AF2" s="7" t="str">
         <f>AH2&amp;" - "&amp;AG2</f>
         <v>MAZDA CX-5 - FTV21M</v>
       </c>
       <c r="AG2" s="7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="AI2" s="7" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="27.6" spans="1:35">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AD3" s="4" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="AE3" s="4" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="AF3" s="4" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AG3" s="4" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AH3" s="4" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="AI3" s="4" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:35">

--- a/cucumber-for-appian/src/test/resources/testdata/End2End/01_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/01_NovatedApp_End2End.xlsx
@@ -3,19 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhana\IdeaProjects\NovatedApp\cucumber-for-appian\src\test\resources\testdata\End2End\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CE1EA6-78C7-4DE4-89D7-0FEED10D8A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0307EE81-8B3C-49F1-8120-8F4AD2648648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="14" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="122">
   <si>
     <t>TC ID</t>
   </si>
@@ -146,33 +146,12 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Toshihiko</t>
-  </si>
-  <si>
     <t>Inafune</t>
   </si>
   <si>
     <t>05 Jun 1995</t>
   </si>
   <si>
-    <t>0469750861</t>
-  </si>
-  <si>
-    <t>inafune@jfcaust.com.au.test</t>
-  </si>
-  <si>
-    <t>JFC Australia Co Pty Ltd</t>
-  </si>
-  <si>
-    <t>FTV21M</t>
-  </si>
-  <si>
-    <t>MAZDA CX-5</t>
-  </si>
-  <si>
-    <t>30 Aug 2029</t>
-  </si>
-  <si>
     <t>TC002</t>
   </si>
   <si>
@@ -320,56 +299,107 @@
     <t>david.cracknell@keyton.com.au.test</t>
   </si>
   <si>
-    <t>21 Parramatta Walk, Craigieburn VIC 3064</t>
-  </si>
-  <si>
     <t>C:\Users\Public\Documents\Invoice.pdf</t>
   </si>
   <si>
     <t>Last Odometer Reading without Km</t>
   </si>
   <si>
+    <t>34 Lookout Way, Tarneit VIC 3029</t>
+  </si>
+  <si>
+    <t>Request Ref Number</t>
+  </si>
+  <si>
+    <t>TC003</t>
+  </si>
+  <si>
+    <t>${TC002.Request Ref Number}</t>
+  </si>
+  <si>
+    <t>MAZDA CX-5 - FTV21M</t>
+  </si>
+  <si>
+    <t>$400.00</t>
+  </si>
+  <si>
+    <t>Submitted By</t>
+  </si>
+  <si>
+    <t>Toshihiko Inafune</t>
+  </si>
+  <si>
+    <t>Updated By</t>
+  </si>
+  <si>
+    <t>ORI-865-472-139-689</t>
+  </si>
+  <si>
+    <t>Last Odometer Reading with km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount </t>
+  </si>
+  <si>
+    <t>${TC001.Amount}</t>
+  </si>
+  <si>
+    <t>BMW IX1</t>
+  </si>
+  <si>
+    <t>Employer ABN</t>
+  </si>
+  <si>
+    <t>${TC001.Employer ABN}</t>
+  </si>
+  <si>
+    <t>Vehicle 1</t>
+  </si>
+  <si>
+    <t>REQ-2593</t>
+  </si>
+  <si>
+    <t>17 Oct 2029</t>
+  </si>
+  <si>
+    <t>626A3A</t>
+  </si>
+  <si>
     <t>Latest Reading (kms)
-8,095 km</t>
-  </si>
-  <si>
-    <t>34 Lookout Way, Tarneit VIC 3029</t>
-  </si>
-  <si>
-    <t>Request Ref Number</t>
-  </si>
-  <si>
-    <t>TC003</t>
-  </si>
-  <si>
-    <t>${TC002.Request Ref Number}</t>
-  </si>
-  <si>
-    <t>MAZDA CX-5 - FTV21M</t>
-  </si>
-  <si>
-    <t>$400.00</t>
-  </si>
-  <si>
-    <t>Submitted By</t>
-  </si>
-  <si>
-    <t>Toshihiko Inafune</t>
-  </si>
-  <si>
-    <t>Updated By</t>
-  </si>
-  <si>
-    <t>ORI-865-472-139-689</t>
-  </si>
-  <si>
-    <t>Last Odometer Reading with km</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amount </t>
-  </si>
-  <si>
-    <t>${TC001.Amount}</t>
+18,065 km</t>
+  </si>
+  <si>
+    <t>BTFWULH</t>
+  </si>
+  <si>
+    <t>ABDGO</t>
+  </si>
+  <si>
+    <t>0469 000 000</t>
+  </si>
+  <si>
+    <t>191799@omsrefresh.com</t>
+  </si>
+  <si>
+    <t>AMP Capital Office and Industrial Pty Ltd</t>
+  </si>
+  <si>
+    <t>44099105094</t>
+  </si>
+  <si>
+    <t>OYMJACPWRXEVYPYGENMAU CARLTON NSW 2218</t>
+  </si>
+  <si>
+    <t>GVNMTQNAABTDB</t>
+  </si>
+  <si>
+    <t>ORI-978-776-970-633</t>
+  </si>
+  <si>
+    <t>ORI-800-221-876-321</t>
+  </si>
+  <si>
+    <t>REQ-733</t>
   </si>
 </sst>
 </file>
@@ -379,12 +409,26 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -412,6 +456,22 @@
       <color rgb="FF1F1F1F"/>
       <name val="Courier New"/>
       <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -452,10 +512,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -463,7 +524,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -476,10 +537,23 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -773,57 +847,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="6.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.25" customWidth="1"/>
-    <col min="5" max="5" width="21.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="21.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.75" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="18.125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.125" customWidth="1"/>
-    <col min="30" max="30" width="18.125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="19.125" customWidth="1"/>
-    <col min="35" max="35" width="18.125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="15" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="12.625" customWidth="1"/>
-    <col min="47" max="47" width="13.5" customWidth="1"/>
-    <col min="48" max="48" width="22" customWidth="1"/>
-    <col min="49" max="49" width="16.625" customWidth="1"/>
-    <col min="50" max="50" width="19.375" customWidth="1"/>
-    <col min="51" max="51" width="21.375" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.75"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="20.125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="22.25"/>
+    <col min="4" max="4" customWidth="true" width="22.25"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="21.75"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="19.375"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="22.25"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="14.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="10" max="10" customWidth="true" width="15.0"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="21.25"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.25"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="21.75"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="14.75"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="19.375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="11.25"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="13.625"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="14.75"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="13.625"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.75"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.75"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" width="18.125"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="14.0"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="14.75"/>
+    <col min="29" max="29" customWidth="true" width="19.125"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="18.125"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="15.875"/>
+    <col min="33" max="34" customWidth="true" width="19.125"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" width="18.125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" width="17.125"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" width="18.25"/>
+    <col min="38" max="38" bestFit="true" customWidth="true" width="20.125"/>
+    <col min="39" max="39" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" width="11.875"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" width="14.0"/>
+    <col min="46" max="46" customWidth="true" width="12.625"/>
+    <col min="47" max="47" customWidth="true" width="13.5"/>
+    <col min="48" max="48" customWidth="true" width="22.0"/>
+    <col min="49" max="49" customWidth="true" width="16.625"/>
+    <col min="50" max="50" customWidth="true" width="19.375"/>
+    <col min="51" max="51" customWidth="true" width="21.375"/>
+    <col min="52" max="52" customWidth="true" width="17.375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" s="1" customFormat="1" ht="40.5">
+    <row r="1" spans="1:52" s="1" customFormat="1" ht="40.5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -833,11 +908,11 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>109</v>
+      <c r="D1" s="11" t="s">
+        <v>100</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>3</v>
@@ -849,7 +924,7 @@
         <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>6</v>
@@ -903,13 +978,13 @@
         <v>22</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="AD1" s="3" t="s">
         <v>23</v>
@@ -924,13 +999,13 @@
         <v>26</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="AK1" s="3" t="s">
         <v>27</v>
@@ -948,37 +1023,40 @@
         <v>31</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>107</v>
+        <v>98</v>
+      </c>
+      <c r="AZ1" s="3" t="s">
+        <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:51" s="2" customFormat="1" ht="40.5">
+    <row r="2" spans="1:52" s="2" customFormat="1" ht="54">
       <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
@@ -986,23 +1064,24 @@
         <v>33</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D2" s="5" t="str">
         <f>SUBSTITUTE(C2,"Latest Reading (kms)","")</f>
         <v xml:space="preserve">
-8,095 km</v>
-      </c>
-      <c r="E2" s="5">
-        <v>8095</v>
-      </c>
-      <c r="F2" s="5">
+18,065 km</v>
+      </c>
+      <c r="E2" s="5" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(CLEAN(D2),"km",""),",","")," ",""),CHAR(160),"")</f>
+        <v>18065</v>
+      </c>
+      <c r="F2" s="5" t="n">
         <f>E2+1</f>
-        <v>8096</v>
-      </c>
-      <c r="G2" s="5">
+        <v>18066.0</v>
+      </c>
+      <c r="G2" s="5" t="n">
         <f>F2</f>
-        <v>8096</v>
+        <v>18066.0</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>34</v>
@@ -1011,10 +1090,10 @@
         <v>400</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>35</v>
@@ -1047,392 +1126,406 @@
         <v>35</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="Y2" s="6" t="str">
         <f>TEXT(G2,"#,##0")&amp;" km"</f>
-        <v>8,096 km</v>
+        <v>18,066 km</v>
       </c>
       <c r="Z2" s="6" t="s">
         <v>36</v>
       </c>
       <c r="AA2" s="6" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="AB2" s="6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="AC2" s="6" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="AD2" s="6" t="str">
         <f>_xlfn.CONCAT(AA2," ",AC2)</f>
-        <v>Toshihiko Inafune</v>
+        <v>BTFWULH ABDGO</v>
       </c>
       <c r="AE2" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG2" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
+      </c>
+      <c r="AF2" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG2" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="AH2" s="6" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="AI2" s="6" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="AJ2" s="6" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="AK2" s="6" t="s">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="AL2" s="6" t="str">
         <f>AN2&amp;" - "&amp;AM2</f>
-        <v>MAZDA CX-5 - FTV21M</v>
+        <v>BMW IX1 - 626A3A</v>
       </c>
       <c r="AM2" s="6" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="AN2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO2" s="6" t="s">
-        <v>45</v>
+        <v>103</v>
+      </c>
+      <c r="AO2" s="10" t="s">
+        <v>108</v>
       </c>
       <c r="AP2" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ2" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="AQ2" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="AR2" s="6"/>
       <c r="AS2" s="6"/>
       <c r="AT2" s="6"/>
       <c r="AU2" s="6"/>
       <c r="AV2" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AW2" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="AW2" s="6" t="s">
+        <v>103</v>
+      </c>
       <c r="AX2" s="6"/>
       <c r="AY2" s="6"/>
+      <c r="AZ2" s="6" t="s">
+        <v>116</v>
+      </c>
     </row>
-    <row r="3" spans="1:51" s="2" customFormat="1" ht="40.5">
+    <row r="3" spans="1:52" s="2" customFormat="1" ht="40.5">
       <c r="A3" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="Z3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="J3" s="4" t="s">
+      <c r="AA3" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB3" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC3" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="AE3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="V3" s="4" t="s">
+      <c r="AF3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="AG3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="AH3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="AJ3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="AL3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AA3" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC3" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD3" s="4" t="s">
+      <c r="AM3" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AE3" s="4" t="s">
+      <c r="AN3" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="AF3" s="4" t="s">
+      <c r="AO3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AG3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="AH3" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ3" s="4" t="s">
+      <c r="AP3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="AK3" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="AL3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM3" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="AN3" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO3" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP3" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="AQ3" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="AR3" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AS3" s="4" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="AT3" s="4" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AU3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV3" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AX3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AY3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AZ3" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" s="2" customFormat="1" ht="40.5">
+      <c r="A4" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="AV3" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AW3" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="AX3" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="AY3" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51" s="2" customFormat="1" ht="40.5">
-      <c r="A4" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="Z4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="J4" s="4" t="s">
+      <c r="AA4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="AE4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="V4" s="4" t="s">
+      <c r="AF4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="AG4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="AH4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="AJ4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Z4" s="4" t="s">
+      <c r="AL4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AA4" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC4" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD4" s="4" t="s">
+      <c r="AM4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AE4" s="4" t="s">
+      <c r="AN4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="AF4" s="4" t="s">
+      <c r="AO4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AG4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="AH4" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ4" s="4" t="s">
+      <c r="AP4" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="AK4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="AL4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="AN4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AO4" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP4" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="AQ4" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="AR4" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AS4" s="4" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="AT4" s="4" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="AU4" s="4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AV4" s="4" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="AW4" s="4" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="AX4" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="AY4" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
+      </c>
+      <c r="AZ4" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:52">
       <c r="G5" s="7"/>
     </row>
-    <row r="10" spans="1:51" ht="14.25">
+    <row r="10" spans="1:52" ht="14.25">
       <c r="X10" s="8"/>
       <c r="AV10" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="AG2" r:id="rId1" xr:uid="{5B0FE663-44B0-4773-BD1C-08E0DE960DB5}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
 </worksheet>

--- a/cucumber-for-appian/src/test/resources/testdata/End2End/01_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/01_NovatedApp_End2End.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="129">
   <si>
     <t>TC ID</t>
   </si>
@@ -400,6 +400,33 @@
   </si>
   <si>
     <t>REQ-733</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+20,778 km</t>
+  </si>
+  <si>
+    <t>0469 000 111</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,079 km</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,196 km</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,197 km</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,198 km</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,201 km</t>
   </si>
 </sst>
 </file>
@@ -1064,24 +1091,24 @@
         <v>33</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="D2" s="5" t="str">
         <f>SUBSTITUTE(C2,"Latest Reading (kms)","")</f>
         <v xml:space="preserve">
-18,065 km</v>
+21,201 km</v>
       </c>
       <c r="E2" s="5" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(CLEAN(D2),"km",""),",","")," ",""),CHAR(160),"")</f>
-        <v>18065</v>
+        <v>21201</v>
       </c>
       <c r="F2" s="5" t="n">
         <f>E2+1</f>
-        <v>18066.0</v>
+        <v>21202.0</v>
       </c>
       <c r="G2" s="5" t="n">
         <f>F2</f>
-        <v>18066.0</v>
+        <v>21202.0</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>34</v>
@@ -1136,7 +1163,7 @@
       </c>
       <c r="Y2" s="6" t="str">
         <f>TEXT(G2,"#,##0")&amp;" km"</f>
-        <v>18,066 km</v>
+        <v>21,202 km</v>
       </c>
       <c r="Z2" s="6" t="s">
         <v>36</v>
@@ -1158,7 +1185,7 @@
         <v>38</v>
       </c>
       <c r="AF2" s="13" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="AG2" s="12" t="s">
         <v>114</v>
